--- a/xlsx/적용_보안설정_ubuntu2404.xlsx
+++ b/xlsx/적용_보안설정_ubuntu2404.xlsx
@@ -1020,7 +1020,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="21" customHeight="1">
+    <row r="26" ht="30" customHeight="1">
       <c r="B26" s="9" t="n"/>
       <c r="C26" s="5" t="n">
         <v>20</v>
@@ -1032,7 +1032,9 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>UID 1000 이상 계정에 90일/7일 정책 소급 적용</t>
+          <t>UID 1000 이상 계정에 90일/7일 정책 소급 적용
+※ 적용 시 즉시 만료되는 계정은 건너뛰고 목록만 안내
+  (서비스 계정 로그인 차단 방지)</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
